--- a/survey_templates/049_social_support_survey--survey_templates.xlsx
+++ b/survey_templates/049_social_support_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat agree'}</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat disagree'}</t>
+          <t>Somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat agree'}</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat disagree'}</t>
+          <t>Somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat agree'}</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat disagree'}</t>
+          <t>Somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
